--- a/artfynd/A 6823-2024 artfynd.xlsx
+++ b/artfynd/A 6823-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6823-2024 artfynd.xlsx
+++ b/artfynd/A 6823-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68598071</v>
+        <v>115201836</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ösjöbäcken, Dlr</t>
+          <t>Ösjöbäcken, Ösjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513909.8768047948</v>
+        <v>513772</v>
       </c>
       <c r="R2" t="n">
-        <v>6699953.939222114</v>
+        <v>6699767</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-26</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-26</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 årets och 1 Förra årets.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,31 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Bo karlstens, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115233595</v>
+        <v>68598071</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,40 +797,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ösjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513771</v>
+        <v>513910</v>
       </c>
       <c r="R3" t="n">
-        <v>6699736</v>
+        <v>6699954</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,17 +861,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2017-08-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2017-08-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>1 årets och 1 Förra årets.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,27 +887,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Bo karlstens, Niklas Rehn</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>115233640</v>
       </c>
       <c r="B4" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,19 +1004,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115233535</v>
+        <v>68508082</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1060,20 +1035,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ösjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513761</v>
+        <v>513651</v>
       </c>
       <c r="R5" t="n">
-        <v>6699800</v>
+        <v>6699850</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,17 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2017-06-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På äldre tall.</t>
+          <t>2017-06-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,75 +1085,70 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Bo karlstens, Niklas Rehn</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115201836</v>
+        <v>115202381</v>
       </c>
       <c r="B6" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ösjöbäcken (Ösjön), Dlr</t>
+          <t>Ösjön, Ösjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513772</v>
+        <v>513771</v>
       </c>
       <c r="R6" t="n">
-        <v>6699767</v>
+        <v>6699720</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,59 +1175,43 @@
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Bo karlstens, Niklas Rehn</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115262770</v>
+        <v>115204355</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1285,22 +1233,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ösjöbäcken, Dlr</t>
+          <t>Ösjön, Ösjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513761</v>
+        <v>513839</v>
       </c>
       <c r="R7" t="n">
-        <v>6699797</v>
+        <v>6699777</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,49 +1277,38 @@
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt på gran, även 5m till tall på stammen.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens, Lars-Erik Nilsson, Niklas Rehn, Anna-Lena Thommson, Börje Eriksson, Samuel Hytter</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115202381</v>
+        <v>115233535</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1396,19 +1330,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ösjön (Ösjön), Dlr</t>
+          <t>Ösjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513771</v>
+        <v>513761</v>
       </c>
       <c r="R8" t="n">
-        <v>6699720</v>
+        <v>6699800</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,43 +1377,44 @@
           <t>2024-03-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Bo karlstens, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115204355</v>
+        <v>115233595</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1498,19 +1436,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ösjön (Ösjön), Dlr</t>
+          <t>Ösjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513839</v>
+        <v>513771</v>
       </c>
       <c r="R9" t="n">
-        <v>6699777</v>
+        <v>6699736</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,82 +1483,81 @@
           <t>2024-03-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Bo karlstens, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115204696</v>
+        <v>115262770</v>
       </c>
       <c r="B10" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ösjön (Ösjön), Dlr</t>
+          <t>ösjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513828</v>
+        <v>513761</v>
       </c>
       <c r="R10" t="n">
-        <v>6699897</v>
+        <v>6699797</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,27 +1589,135 @@
           <t>2024-03-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt på gran, även 5m till tall på stammen.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Lars-Erik Nilsson, Niklas Rehn, Anna-Lena Thommson, Börje Eriksson, Samuel Hytter</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115204696</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ösjön, Ösjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>513828</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6699897</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Niklas Rehn</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Niklas Rehn</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6823-2024 artfynd.xlsx
+++ b/artfynd/A 6823-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115201836</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68598071</t>
         </is>
       </c>
     </row>
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115233640</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68508082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115202381</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115204355</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115233535</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115233595</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115262770</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,8 +1768,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115204696</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>